--- a/skills/admissions-hwpx-xlsx/assets/fixed-application-tracker.xlsx
+++ b/skills/admissions-hwpx-xlsx/assets/fixed-application-tracker.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신청학과 취업·진학 실적" sheetId="1" r:id="R70a4946603af4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신청학과 취업·진학 실적" sheetId="1" r:id="R0ec768a9121149aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,6 +22,15 @@
     <x:t xml:space="preserve">학과</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">제출 서류</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">조건/주의 사항</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">마감</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">전형</x:t>
   </x:si>
   <x:si>
@@ -32,6 +41,12 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">비고란</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">서류제출</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">우편마감</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">여부</x:t>
@@ -45,7 +60,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="1">
-    <x:numFmt numFmtId="180" formatCode="m&quot;월&quot;\ d&quot;일&quot;;@"/>
+    <x:numFmt numFmtId="176" formatCode="m&quot;월&quot;\ d&quot;일&quot;;@"/>
   </x:numFmts>
   <x:fonts count="8">
     <x:font>
@@ -110,7 +125,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="5">
     <x:border/>
     <x:border/>
     <x:border>
@@ -123,6 +138,28 @@
       <x:top style="thin">
         <x:color indexed="64"/>
       </x:top>
+      <x:bottom style="thin">
+        <x:color indexed="64"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color indexed="64"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color indexed="64"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color indexed="64"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color indexed="64"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color indexed="64"/>
+      </x:right>
       <x:bottom style="thin">
         <x:color indexed="64"/>
       </x:bottom>
@@ -132,54 +169,75 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="180" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="180" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -387,64 +445,80 @@
     <x:col min="1" max="1" width="10.625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="13.875" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="35" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="48.25" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="10.5" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="10.625" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="11.75" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <x:col min="9" max="9" width="10.25" style="1" customWidth="1"/>
-    <x:col min="10" max="10" width="8.125" style="1" customWidth="1"/>
-    <x:col min="11" max="11" width="10.25" style="1" customWidth="1"/>
-    <x:col min="12" max="12" width="9" style="1" customWidth="0"/>
+    <x:col min="4" max="4" width="46" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="40.375" style="1" customWidth="1"/>
+    <x:col min="6" max="7" width="35.625" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="48.25" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="10.5" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="10.625" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="11.75" style="1" customWidth="1"/>
+    <x:col min="12" max="12" width="10.625" style="1" customWidth="1"/>
     <x:col min="13" max="13" width="10.25" style="1" customWidth="1"/>
-    <x:col min="14" max="16384" width="9" style="1" customWidth="0"/>
+    <x:col min="14" max="14" width="8.125" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="10.25" style="1" customWidth="1"/>
+    <x:col min="16" max="16" width="9" style="1" customWidth="0"/>
+    <x:col min="17" max="17" width="10.25" style="1" customWidth="1"/>
+    <x:col min="18" max="16384" width="9" style="1" customWidth="0"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="D1" s="7"/>
-      <x:c r="E1" s="7"/>
-      <x:c r="F1" s="7"/>
-      <x:c r="G1" s="7"/>
+      <x:c r="D1" s="18"/>
     </x:row>
     <x:row r="2" ht="3" customHeight="1">
-      <x:c r="A2" s="2"/>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="8"/>
-      <x:c r="E2" s="8"/>
-      <x:c r="F2" s="8"/>
-      <x:c r="G2" s="8"/>
+      <x:c r="A2" s="16"/>
+      <x:c r="B2" s="16"/>
+      <x:c r="C2" s="16"/>
+      <x:c r="D2" s="19"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
     </x:row>
     <x:row r="3" ht="35.25" customHeight="1">
-      <x:c r="A3" s="6" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B3" s="5" t="str">
+      <x:c r="B3" s="15" t="str">
         <x:v>[지원자명] 지원 대학</x:v>
       </x:c>
-      <x:c r="C3" s="5"/>
-      <x:c r="D3" s="9"/>
-      <x:c r="E3" s="9"/>
-      <x:c r="F3" s="9"/>
-      <x:c r="G3" s="9"/>
+      <x:c r="C3" s="15"/>
+      <x:c r="D3" s="20"/>
+      <x:c r="E3" s="5"/>
+      <x:c r="F3" s="5"/>
+      <x:c r="G3" s="5"/>
+      <x:c r="H3" s="5"/>
+      <x:c r="I3" s="5"/>
+      <x:c r="J3" s="5"/>
+      <x:c r="K3" s="5"/>
     </x:row>
     <x:row r="4" ht="3" customHeight="1">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="3"/>
-      <x:c r="C4" s="3"/>
-      <x:c r="D4" s="10"/>
-      <x:c r="E4" s="10"/>
-      <x:c r="F4" s="10"/>
-      <x:c r="G4" s="10"/>
+      <x:c r="A4" s="17"/>
+      <x:c r="B4" s="17"/>
+      <x:c r="C4" s="17"/>
+      <x:c r="D4" s="21"/>
+      <x:c r="E4" s="6"/>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
     </x:row>
     <x:row r="5" ht="9.949999809265137" customHeight="1">
-      <x:c r="A5" s="4"/>
-      <x:c r="B5" s="4"/>
-      <x:c r="C5" s="4"/>
-      <x:c r="D5" s="11"/>
-      <x:c r="E5" s="11"/>
-      <x:c r="F5" s="11"/>
-      <x:c r="G5" s="11"/>
+      <x:c r="A5" s="2"/>
+      <x:c r="B5" s="2"/>
+      <x:c r="C5" s="2"/>
+      <x:c r="D5" s="22"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+      <x:c r="I5" s="2"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2"/>
     </x:row>
     <x:row r="6" ht="20.100000381469727" customHeight="1">
       <x:c r="A6" s="14" t="s">
@@ -456,10 +530,10 @@
       <x:c r="C6" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="s">
+      <x:c r="D6" s="23" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="s">
+      <x:c r="E6" s="23" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="14" t="s">
@@ -469,132 +543,177 @@
       <x:c r="H6" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I6" s="12"/>
-      <x:c r="J6" s="12"/>
-      <x:c r="K6" s="12"/>
-      <x:c r="L6" s="12"/>
-      <x:c r="M6" s="12"/>
+      <x:c r="I6" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K6" s="14"/>
+      <x:c r="L6" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M6" s="7"/>
+      <x:c r="N6" s="7"/>
+      <x:c r="O6" s="7"/>
+      <x:c r="P6" s="7"/>
+      <x:c r="Q6" s="7"/>
     </x:row>
     <x:row r="7" ht="20.100000381469727" customHeight="1">
       <x:c r="A7" s="14"/>
       <x:c r="B7" s="14"/>
       <x:c r="C7" s="14"/>
-      <x:c r="D7" s="14"/>
-      <x:c r="E7" s="14"/>
-      <x:c r="F7" s="15" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G7" s="15" t="s">
-        <x:v>9</x:v>
+      <x:c r="D7" s="24"/>
+      <x:c r="E7" s="24"/>
+      <x:c r="F7" s="9" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H7" s="14"/>
-      <x:c r="I7" s="12"/>
-      <x:c r="J7" s="12"/>
-      <x:c r="K7" s="12"/>
-      <x:c r="L7" s="12"/>
-      <x:c r="M7" s="12"/>
-    </x:row>
-    <x:row r="8" ht="27.950000762939453" customHeight="1">
-      <x:c r="A8" s="13"/>
-      <x:c r="B8" s="13"/>
-      <x:c r="C8" s="17"/>
-      <x:c r="D8" s="17"/>
-      <x:c r="E8" s="19"/>
-      <x:c r="F8" s="16"/>
-      <x:c r="H8" s="16"/>
-      <x:c r="I8" s="12"/>
-      <x:c r="J8" s="12"/>
-      <x:c r="K8" s="12"/>
-      <x:c r="L8" s="12"/>
-      <x:c r="M8" s="12"/>
-    </x:row>
-    <x:row r="9" ht="27.950000762939453" customHeight="1">
-      <x:c r="A9" s="13"/>
-      <x:c r="B9" s="13"/>
-      <x:c r="C9" s="17"/>
-      <x:c r="D9" s="17"/>
-      <x:c r="E9" s="19"/>
-      <x:c r="F9" s="16"/>
-      <x:c r="G9" s="18"/>
-      <x:c r="H9" s="16"/>
-      <x:c r="I9" s="12"/>
-      <x:c r="J9" s="12"/>
+      <x:c r="I7" s="14"/>
+      <x:c r="J7" s="9" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K7" s="9" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L7" s="14"/>
+      <x:c r="M7" s="7"/>
+      <x:c r="N7" s="7"/>
+      <x:c r="O7" s="7"/>
+      <x:c r="P7" s="7"/>
+      <x:c r="Q7" s="7"/>
+    </x:row>
+    <x:row r="8" ht="74.25" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="8"/>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="25"/>
+      <x:c r="E8" s="26"/>
+      <x:c r="F8" s="25"/>
+      <x:c r="G8" s="25"/>
+      <x:c r="H8" s="11"/>
+      <x:c r="I8" s="13"/>
+      <x:c r="J8" s="10"/>
+      <x:c r="L8" s="10"/>
+      <x:c r="M8" s="7"/>
+      <x:c r="N8" s="7"/>
+      <x:c r="O8" s="7"/>
+      <x:c r="P8" s="7"/>
+      <x:c r="Q8" s="7"/>
+    </x:row>
+    <x:row r="9" ht="74.25" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="8"/>
+      <x:c r="C9" s="11"/>
+      <x:c r="D9" s="25"/>
+      <x:c r="E9" s="26"/>
+      <x:c r="F9" s="25"/>
+      <x:c r="G9" s="25"/>
+      <x:c r="H9" s="11"/>
+      <x:c r="I9" s="13"/>
+      <x:c r="J9" s="10"/>
       <x:c r="K9" s="12"/>
-      <x:c r="L9" s="12"/>
-      <x:c r="M9" s="12"/>
-    </x:row>
-    <x:row r="10" ht="27.950000762939453" customHeight="1">
-      <x:c r="A10" s="13"/>
-      <x:c r="B10" s="13"/>
-      <x:c r="C10" s="17"/>
-      <x:c r="D10" s="17"/>
-      <x:c r="E10" s="19"/>
-      <x:c r="F10" s="16"/>
-      <x:c r="G10" s="16"/>
-      <x:c r="H10" s="16"/>
-      <x:c r="I10" s="12"/>
-      <x:c r="J10" s="12"/>
-      <x:c r="K10" s="12"/>
-      <x:c r="L10" s="12"/>
-      <x:c r="M10" s="12"/>
-    </x:row>
-    <x:row r="11" ht="27.950000762939453" customHeight="1">
-      <x:c r="A11" s="13"/>
-      <x:c r="B11" s="13"/>
-      <x:c r="C11" s="17"/>
-      <x:c r="D11" s="17"/>
-      <x:c r="E11" s="19"/>
-      <x:c r="F11" s="16"/>
-      <x:c r="G11" s="16"/>
-      <x:c r="H11" s="16"/>
-      <x:c r="I11" s="12"/>
-      <x:c r="J11" s="12"/>
-      <x:c r="K11" s="12"/>
-      <x:c r="L11" s="12"/>
-      <x:c r="M11" s="12"/>
-    </x:row>
-    <x:row r="12" ht="27.950000762939453" customHeight="1">
-      <x:c r="A12" s="13"/>
-      <x:c r="B12" s="13"/>
-      <x:c r="C12" s="17"/>
-      <x:c r="D12" s="17"/>
-      <x:c r="E12" s="19"/>
-      <x:c r="F12" s="16"/>
-      <x:c r="G12" s="16"/>
-      <x:c r="H12" s="16"/>
-      <x:c r="I12" s="12"/>
-      <x:c r="J12" s="12"/>
-      <x:c r="K12" s="12"/>
-      <x:c r="L12" s="12"/>
-      <x:c r="M12" s="12"/>
-    </x:row>
-    <x:row r="13" ht="27.950000762939453" customHeight="1">
-      <x:c r="A13" s="13"/>
-      <x:c r="B13" s="13"/>
-      <x:c r="C13" s="17"/>
-      <x:c r="D13" s="17"/>
-      <x:c r="E13" s="19"/>
-      <x:c r="F13" s="16"/>
-      <x:c r="G13" s="16"/>
-      <x:c r="H13" s="16"/>
-      <x:c r="I13" s="12"/>
-      <x:c r="J13" s="12"/>
-      <x:c r="K13" s="12"/>
-      <x:c r="L13" s="12"/>
-      <x:c r="M13" s="12"/>
+      <x:c r="L9" s="10"/>
+      <x:c r="M9" s="7"/>
+      <x:c r="N9" s="7"/>
+      <x:c r="O9" s="7"/>
+      <x:c r="P9" s="7"/>
+      <x:c r="Q9" s="7"/>
+    </x:row>
+    <x:row r="10" ht="74.25" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="8"/>
+      <x:c r="C10" s="11"/>
+      <x:c r="D10" s="26"/>
+      <x:c r="E10" s="26"/>
+      <x:c r="F10" s="25"/>
+      <x:c r="G10" s="25"/>
+      <x:c r="H10" s="11"/>
+      <x:c r="I10" s="13"/>
+      <x:c r="J10" s="10"/>
+      <x:c r="K10" s="10"/>
+      <x:c r="L10" s="10"/>
+      <x:c r="M10" s="7"/>
+      <x:c r="N10" s="7"/>
+      <x:c r="O10" s="7"/>
+      <x:c r="P10" s="7"/>
+      <x:c r="Q10" s="7"/>
+    </x:row>
+    <x:row r="11" ht="74.25" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="8"/>
+      <x:c r="C11" s="11"/>
+      <x:c r="D11" s="26"/>
+      <x:c r="E11" s="26"/>
+      <x:c r="F11" s="25"/>
+      <x:c r="G11" s="25"/>
+      <x:c r="H11" s="11"/>
+      <x:c r="I11" s="13"/>
+      <x:c r="J11" s="10"/>
+      <x:c r="K11" s="10"/>
+      <x:c r="L11" s="10"/>
+      <x:c r="M11" s="7"/>
+      <x:c r="N11" s="7"/>
+      <x:c r="O11" s="7"/>
+      <x:c r="P11" s="7"/>
+      <x:c r="Q11" s="7"/>
+    </x:row>
+    <x:row r="12" ht="74.25" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="8"/>
+      <x:c r="C12" s="11"/>
+      <x:c r="D12" s="26"/>
+      <x:c r="E12" s="26"/>
+      <x:c r="F12" s="25"/>
+      <x:c r="G12" s="25"/>
+      <x:c r="H12" s="11"/>
+      <x:c r="I12" s="13"/>
+      <x:c r="J12" s="10"/>
+      <x:c r="K12" s="10"/>
+      <x:c r="L12" s="10"/>
+      <x:c r="M12" s="7"/>
+      <x:c r="N12" s="7"/>
+      <x:c r="O12" s="7"/>
+      <x:c r="P12" s="7"/>
+      <x:c r="Q12" s="7"/>
+    </x:row>
+    <x:row r="13" ht="74.25" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="8"/>
+      <x:c r="C13" s="11"/>
+      <x:c r="D13" s="26"/>
+      <x:c r="E13" s="26"/>
+      <x:c r="F13" s="25"/>
+      <x:c r="G13" s="25"/>
+      <x:c r="H13" s="11"/>
+      <x:c r="I13" s="13"/>
+      <x:c r="J13" s="10"/>
+      <x:c r="K13" s="10"/>
+      <x:c r="L13" s="10"/>
+      <x:c r="M13" s="7"/>
+      <x:c r="N13" s="7"/>
+      <x:c r="O13" s="7"/>
+      <x:c r="P13" s="7"/>
+      <x:c r="Q13" s="7"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="H6:H7"/>
-    <x:mergeCell ref="F6:G6"/>
+    <x:mergeCell ref="L6:L7"/>
+    <x:mergeCell ref="J6:K6"/>
     <x:mergeCell ref="B3:C3"/>
     <x:mergeCell ref="A2:C2"/>
     <x:mergeCell ref="A4:C4"/>
-    <x:mergeCell ref="E6:E7"/>
+    <x:mergeCell ref="I6:I7"/>
     <x:mergeCell ref="A6:A7"/>
     <x:mergeCell ref="B6:B7"/>
     <x:mergeCell ref="C6:C7"/>
+    <x:mergeCell ref="H6:H7"/>
     <x:mergeCell ref="D6:D7"/>
+    <x:mergeCell ref="E6:E7"/>
+    <x:mergeCell ref="F6:G6"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
